--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D9F3123-6B15-0D46-8914-8973C9290F60}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{992ED7EE-D3C1-D945-892E-5ADFE210E698}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-120" windowWidth="36500" windowHeight="14900" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="340" yWindow="-17560" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -213,9 +213,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>12090135</v>
+        <v>11237387</v>
       </c>
       <c r="J2" s="2">
         <v>630566</v>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{992ED7EE-D3C1-D945-892E-5ADFE210E698}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97F56976-1DC5-6745-AB7B-49FEA0D446C9}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="-17560" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="820" yWindow="-10700" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -647,7 +647,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="2">
-        <v>249541</v>
+        <v>334817</v>
       </c>
       <c r="C2">
         <v>0</v>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97F56976-1DC5-6745-AB7B-49FEA0D446C9}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A506EE72-A6F8-6C42-BF1A-1C532753F708}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="-10700" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="880" yWindow="-19400" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>prep_oral</t>
   </si>
@@ -123,13 +123,20 @@
   </si>
   <si>
     <t>Mozambique</t>
+  </si>
+  <si>
+    <t>Zambia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -143,6 +150,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,18 +226,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -554,6 +591,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -721,7 +759,78 @@
       <c r="AB2" s="5"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6">
+        <v>133901</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1624</v>
+      </c>
+      <c r="D3" s="6">
+        <v>274325</v>
+      </c>
+      <c r="F3" s="8">
+        <v>6454</v>
+      </c>
+      <c r="G3">
+        <v>74</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>3671497</v>
+      </c>
+      <c r="J3" s="9">
+        <v>291365</v>
+      </c>
+      <c r="K3" s="9">
+        <v>516869</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>76</v>
+      </c>
+      <c r="P3" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>24</v>
+      </c>
+      <c r="R3">
+        <v>79</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>96</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>95</v>
+      </c>
+      <c r="X3">
+        <v>95</v>
+      </c>
+      <c r="AA3">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A506EE72-A6F8-6C42-BF1A-1C532753F708}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD2A679-0C38-2647-B118-D5134FCA8CF7}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="-19400" windowWidth="28800" windowHeight="17400" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="2380" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2310EEF3-F49B-1740-9531-F7745180ADE8}</author>
+    <author>tc={D2460033-F738-7142-809A-6A6DE4B461DC}</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{2310EEF3-F49B-1740-9531-F7745180ADE8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Community-Based HIV Test in 2025</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{D2460033-F738-7142-809A-6A6DE4B461DC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    90% HIV Ascertainment in STI services</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>prep_oral</t>
   </si>
@@ -126,6 +153,9 @@
   </si>
   <si>
     <t>Zambia</t>
+  </si>
+  <si>
+    <t>Malawi</t>
   </si>
 </sst>
 </file>
@@ -136,7 +166,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -162,6 +192,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -230,7 +272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -252,6 +294,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -268,6 +313,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="John Phiri" id="{5C421396-DDD7-7544-B72E-8164399E8CC5}" userId="S::jphiri@hivmw.org::153ac18e-b8b8-4307-ae1e-382ef26ad919" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -585,12 +636,24 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{2310EEF3-F49B-1740-9531-F7745180ADE8}">
+    <text>Community-Based HIV Test in 2025</text>
+  </threadedComment>
+  <threadedComment ref="L4" dT="2026-06-05T07:06:08.87" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{D2460033-F738-7142-809A-6A6DE4B461DC}">
+    <text>90% HIV Ascertainment in STI services</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
   <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -833,7 +896,75 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="11">
+        <v>58089</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>47890</v>
+      </c>
+      <c r="E4" s="11">
+        <v>139000000</v>
+      </c>
+      <c r="F4" s="12">
+        <v>32466</v>
+      </c>
+      <c r="G4" s="13">
+        <v>91</v>
+      </c>
+      <c r="H4" s="11">
+        <v>30762</v>
+      </c>
+      <c r="I4" s="11">
+        <v>3569803</v>
+      </c>
+      <c r="J4" s="11">
+        <v>129230</v>
+      </c>
+      <c r="K4" s="11">
+        <v>129013</v>
+      </c>
+      <c r="L4" s="11">
+        <v>513183</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1741863</v>
+      </c>
+      <c r="N4" s="11">
+        <v>60432</v>
+      </c>
+      <c r="O4" s="13">
+        <v>88</v>
+      </c>
+      <c r="P4" s="13">
+        <v>96</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>82</v>
+      </c>
+      <c r="S4">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>46</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
+        <v>57</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -912,5 +1043,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD2A679-0C38-2647-B118-D5134FCA8CF7}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6366DBA1-D603-C648-9C2E-09200EDD45C1}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,8 +63,35 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={214082FE-14FA-0647-801D-F9AB7F48F848}</author>
+    <author>tc={9EA61213-9245-144C-A1BB-47FC06915A74}</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{214082FE-14FA-0647-801D-F9AB7F48F848}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Community-Based HIV Test in 2025</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{9EA61213-9245-144C-A1BB-47FC06915A74}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    90% HIV Ascertainment in STI services</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>prep_oral</t>
   </si>
@@ -272,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -297,6 +325,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -647,6 +676,17 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{214082FE-14FA-0647-801D-F9AB7F48F848}">
+    <text>Community-Based HIV Test in 2025</text>
+  </threadedComment>
+  <threadedComment ref="L4" dT="2026-06-05T07:06:08.87" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{9EA61213-9245-144C-A1BB-47FC06915A74}">
+    <text>90% HIV Ascertainment in STI services</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
   <dimension ref="A1:AB29"/>
@@ -759,9 +799,6 @@
       <c r="E2">
         <v>159303077</v>
       </c>
-      <c r="G2">
-        <v>98</v>
-      </c>
       <c r="H2">
         <v>0</v>
       </c>
@@ -883,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W3">
         <v>95</v>
@@ -968,6 +1005,460 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42369831-8138-B640-8215-2EE7ACAC45E9}">
+  <dimension ref="A1:AB29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2">
+        <v>334817</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>147928</v>
+      </c>
+      <c r="E2">
+        <v>159303077</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>11237387</v>
+      </c>
+      <c r="J2" s="2">
+        <v>630566</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1064884</v>
+      </c>
+      <c r="L2" s="2">
+        <v>222182</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1322885</v>
+      </c>
+      <c r="O2" s="4">
+        <v>90</v>
+      </c>
+      <c r="P2" s="4">
+        <v>95</v>
+      </c>
+      <c r="R2" s="5">
+        <v>67</v>
+      </c>
+      <c r="S2" s="5">
+        <v>37</v>
+      </c>
+      <c r="T2" s="5">
+        <v>40</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="V2" s="5">
+        <v>2</v>
+      </c>
+      <c r="W2" s="5">
+        <v>50</v>
+      </c>
+      <c r="X2" s="5">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>77</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>80</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6">
+        <v>133901</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1624</v>
+      </c>
+      <c r="D3" s="6">
+        <v>274325</v>
+      </c>
+      <c r="F3" s="8">
+        <v>6454</v>
+      </c>
+      <c r="G3">
+        <v>74</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>3671497</v>
+      </c>
+      <c r="J3" s="9">
+        <v>291365</v>
+      </c>
+      <c r="K3" s="9">
+        <v>516869</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>76</v>
+      </c>
+      <c r="P3" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>24</v>
+      </c>
+      <c r="R3">
+        <v>79</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>96</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>30</v>
+      </c>
+      <c r="W3">
+        <v>95</v>
+      </c>
+      <c r="X3">
+        <v>95</v>
+      </c>
+      <c r="AA3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="11">
+        <v>58089</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>47890</v>
+      </c>
+      <c r="E4" s="11">
+        <v>139000000</v>
+      </c>
+      <c r="F4" s="12">
+        <v>32466</v>
+      </c>
+      <c r="G4" s="13">
+        <v>91</v>
+      </c>
+      <c r="H4" s="11">
+        <v>30762</v>
+      </c>
+      <c r="I4" s="11">
+        <v>3569803</v>
+      </c>
+      <c r="J4" s="11">
+        <v>129230</v>
+      </c>
+      <c r="K4" s="11">
+        <v>129013</v>
+      </c>
+      <c r="L4" s="11">
+        <v>513183</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1741863</v>
+      </c>
+      <c r="N4" s="11">
+        <v>60432</v>
+      </c>
+      <c r="O4" s="13">
+        <v>88</v>
+      </c>
+      <c r="P4" s="13">
+        <v>96</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>82</v>
+      </c>
+      <c r="S4">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>46</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="O5" s="14">
+        <f>AVERAGE(O2:O4)</f>
+        <v>84.666666666666671</v>
+      </c>
+      <c r="P5" s="14">
+        <f t="shared" ref="P5:AB5" si="0">AVERAGE(P2:P4)</f>
+        <v>94.666666666666671</v>
+      </c>
+      <c r="Q5" s="14">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R5" s="14">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" si="0"/>
+        <v>29.333333333333332</v>
+      </c>
+      <c r="T5" s="14">
+        <f t="shared" si="0"/>
+        <v>60.666666666666664</v>
+      </c>
+      <c r="U5" s="14">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="V5" s="14">
+        <f t="shared" si="0"/>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="W5" s="14">
+        <f t="shared" si="0"/>
+        <v>72.5</v>
+      </c>
+      <c r="X5" s="14">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="Y5" s="14">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="Z5" s="14">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="AA5" s="14">
+        <f t="shared" si="0"/>
+        <v>45.333333333333336</v>
+      </c>
+      <c r="AB5" s="14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6366DBA1-D603-C648-9C2E-09200EDD45C1}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BED207BC-5D2F-8141-8707-072E6AF2FE8F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>prep_oral</t>
   </si>
@@ -184,6 +184,12 @@
   </si>
   <si>
     <t>Malawi</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>South Africa</t>
   </si>
 </sst>
 </file>
@@ -194,7 +200,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -226,12 +232,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1402,66 +1402,71 @@
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>6631</v>
+      </c>
+      <c r="D5">
+        <v>3639</v>
+      </c>
+      <c r="G5">
+        <v>97</v>
+      </c>
+      <c r="I5">
+        <v>302749</v>
+      </c>
+      <c r="J5">
+        <v>4058</v>
+      </c>
+      <c r="N5">
+        <v>18513</v>
+      </c>
       <c r="O5" s="14">
-        <f>AVERAGE(O2:O4)</f>
-        <v>84.666666666666671</v>
+        <v>90</v>
       </c>
       <c r="P5" s="14">
-        <f t="shared" ref="P5:AB5" si="0">AVERAGE(P2:P4)</f>
-        <v>94.666666666666671</v>
-      </c>
-      <c r="Q5" s="14">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="Q5" s="14"/>
       <c r="R5" s="14">
-        <f t="shared" si="0"/>
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="S5" s="14">
-        <f t="shared" si="0"/>
-        <v>29.333333333333332</v>
+        <v>56</v>
       </c>
       <c r="T5" s="14">
-        <f t="shared" si="0"/>
-        <v>60.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="U5" s="14">
-        <f t="shared" si="0"/>
-        <v>3.3333333333333333E-2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="14">
-        <f t="shared" si="0"/>
-        <v>12.333333333333334</v>
-      </c>
-      <c r="W5" s="14">
-        <f t="shared" si="0"/>
-        <v>72.5</v>
-      </c>
-      <c r="X5" s="14">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="Y5" s="14">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="Z5" s="14">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
       <c r="AA5" s="14">
-        <f t="shared" si="0"/>
-        <v>45.333333333333336</v>
-      </c>
-      <c r="AB5" s="14" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AB5" s="14"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6">
+        <v>95</v>
+      </c>
+      <c r="T6">
+        <v>5</v>
+      </c>
+      <c r="AA6">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{BF29F2F3-1EB6-8046-A3DB-FBA4844A21DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BED207BC-5D2F-8141-8707-072E6AF2FE8F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98AE077-C375-0E4D-89BD-544B6E37D2D2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,6 +37,33 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={214082FE-14FA-0647-801D-F9AB7F48F848}</author>
+    <author>tc={9EA61213-9245-144C-A1BB-47FC06915A74}</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{214082FE-14FA-0647-801D-F9AB7F48F848}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Community-Based HIV Test in 2025</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{9EA61213-9245-144C-A1BB-47FC06915A74}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    90% HIV Ascertainment in STI services</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={2310EEF3-F49B-1740-9531-F7745180ADE8}</author>
@@ -63,35 +90,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={214082FE-14FA-0647-801D-F9AB7F48F848}</author>
-    <author>tc={9EA61213-9245-144C-A1BB-47FC06915A74}</author>
-  </authors>
-  <commentList>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{214082FE-14FA-0647-801D-F9AB7F48F848}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Community-Based HIV Test in 2025</t>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{9EA61213-9245-144C-A1BB-47FC06915A74}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    90% HIV Ascertainment in STI services</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>prep_oral</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>South Africa</t>
+  </si>
+  <si>
+    <t>Eswatini</t>
   </si>
 </sst>
 </file>
@@ -667,6 +670,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{214082FE-14FA-0647-801D-F9AB7F48F848}">
+    <text>Community-Based HIV Test in 2025</text>
+  </threadedComment>
+  <threadedComment ref="L4" dT="2026-06-05T07:06:08.87" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{9EA61213-9245-144C-A1BB-47FC06915A74}">
+    <text>90% HIV Ascertainment in STI services</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{2310EEF3-F49B-1740-9531-F7745180ADE8}">
     <text>Community-Based HIV Test in 2025</text>
   </threadedComment>
@@ -676,415 +690,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{214082FE-14FA-0647-801D-F9AB7F48F848}">
-    <text>Community-Based HIV Test in 2025</text>
-  </threadedComment>
-  <threadedComment ref="L4" dT="2026-06-05T07:06:08.87" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{9EA61213-9245-144C-A1BB-47FC06915A74}">
-    <text>90% HIV Ascertainment in STI services</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
-  <dimension ref="A1:AB29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="2">
-        <v>334817</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>147928</v>
-      </c>
-      <c r="E2">
-        <v>159303077</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>11237387</v>
-      </c>
-      <c r="J2" s="2">
-        <v>630566</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1064884</v>
-      </c>
-      <c r="L2" s="2">
-        <v>222182</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>1322885</v>
-      </c>
-      <c r="O2" s="4">
-        <v>90</v>
-      </c>
-      <c r="P2" s="4">
-        <v>95</v>
-      </c>
-      <c r="R2" s="5">
-        <v>67</v>
-      </c>
-      <c r="S2" s="5">
-        <v>37</v>
-      </c>
-      <c r="T2" s="5">
-        <v>40</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="V2" s="5">
-        <v>2</v>
-      </c>
-      <c r="W2" s="5">
-        <v>50</v>
-      </c>
-      <c r="X2" s="5">
-        <v>85</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>77</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>80</v>
-      </c>
-      <c r="AA2" s="5">
-        <v>24</v>
-      </c>
-      <c r="AB2" s="5"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6">
-        <v>133901</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1624</v>
-      </c>
-      <c r="D3" s="6">
-        <v>274325</v>
-      </c>
-      <c r="F3" s="8">
-        <v>6454</v>
-      </c>
-      <c r="G3">
-        <v>74</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>3671497</v>
-      </c>
-      <c r="J3" s="9">
-        <v>291365</v>
-      </c>
-      <c r="K3" s="9">
-        <v>516869</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>76</v>
-      </c>
-      <c r="P3" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>24</v>
-      </c>
-      <c r="R3">
-        <v>79</v>
-      </c>
-      <c r="S3">
-        <v>4</v>
-      </c>
-      <c r="T3">
-        <v>96</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>30</v>
-      </c>
-      <c r="W3">
-        <v>95</v>
-      </c>
-      <c r="X3">
-        <v>95</v>
-      </c>
-      <c r="AA3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="11">
-        <v>58089</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11">
-        <v>47890</v>
-      </c>
-      <c r="E4" s="11">
-        <v>139000000</v>
-      </c>
-      <c r="F4" s="12">
-        <v>32466</v>
-      </c>
-      <c r="G4" s="13">
-        <v>91</v>
-      </c>
-      <c r="H4" s="11">
-        <v>30762</v>
-      </c>
-      <c r="I4" s="11">
-        <v>3569803</v>
-      </c>
-      <c r="J4" s="11">
-        <v>129230</v>
-      </c>
-      <c r="K4" s="11">
-        <v>129013</v>
-      </c>
-      <c r="L4" s="11">
-        <v>513183</v>
-      </c>
-      <c r="M4" s="11">
-        <v>1741863</v>
-      </c>
-      <c r="N4" s="11">
-        <v>60432</v>
-      </c>
-      <c r="O4" s="13">
-        <v>88</v>
-      </c>
-      <c r="P4" s="13">
-        <v>96</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>15</v>
-      </c>
-      <c r="R4">
-        <v>82</v>
-      </c>
-      <c r="S4">
-        <v>47</v>
-      </c>
-      <c r="T4">
-        <v>46</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="AA4">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42369831-8138-B640-8215-2EE7ACAC45E9}">
   <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1469,6 +1075,457 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>25694</v>
+      </c>
+      <c r="C7">
+        <v>302</v>
+      </c>
+      <c r="D7">
+        <v>1438</v>
+      </c>
+      <c r="I7">
+        <v>175431</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>32160</v>
+      </c>
+      <c r="N7">
+        <f>91886-M7</f>
+        <v>59726</v>
+      </c>
+      <c r="P7">
+        <v>95</v>
+      </c>
+      <c r="R7">
+        <v>92.2</v>
+      </c>
+      <c r="S7">
+        <v>49.5</v>
+      </c>
+      <c r="T7">
+        <v>28.4</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AA7">
+        <v>64.2</v>
+      </c>
+      <c r="AB7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
+  <dimension ref="A1:AB29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2">
+        <v>334817</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>147928</v>
+      </c>
+      <c r="E2">
+        <v>159303077</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>11237387</v>
+      </c>
+      <c r="J2" s="2">
+        <v>630566</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1064884</v>
+      </c>
+      <c r="L2" s="2">
+        <v>222182</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1322885</v>
+      </c>
+      <c r="O2" s="4">
+        <v>90</v>
+      </c>
+      <c r="P2" s="4">
+        <v>95</v>
+      </c>
+      <c r="R2" s="5">
+        <v>67</v>
+      </c>
+      <c r="S2" s="5">
+        <v>37</v>
+      </c>
+      <c r="T2" s="5">
+        <v>40</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="V2" s="5">
+        <v>2</v>
+      </c>
+      <c r="W2" s="5">
+        <v>50</v>
+      </c>
+      <c r="X2" s="5">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>77</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>80</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6">
+        <v>133901</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1624</v>
+      </c>
+      <c r="D3" s="6">
+        <v>274325</v>
+      </c>
+      <c r="F3" s="8">
+        <v>6454</v>
+      </c>
+      <c r="G3">
+        <v>74</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>3671497</v>
+      </c>
+      <c r="J3" s="9">
+        <v>291365</v>
+      </c>
+      <c r="K3" s="9">
+        <v>516869</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>76</v>
+      </c>
+      <c r="P3" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>24</v>
+      </c>
+      <c r="R3">
+        <v>79</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>96</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>30</v>
+      </c>
+      <c r="W3">
+        <v>95</v>
+      </c>
+      <c r="X3">
+        <v>95</v>
+      </c>
+      <c r="AA3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="11">
+        <v>58089</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>47890</v>
+      </c>
+      <c r="E4" s="11">
+        <v>139000000</v>
+      </c>
+      <c r="F4" s="12">
+        <v>32466</v>
+      </c>
+      <c r="G4" s="13">
+        <v>91</v>
+      </c>
+      <c r="H4" s="11">
+        <v>30762</v>
+      </c>
+      <c r="I4" s="11">
+        <v>3569803</v>
+      </c>
+      <c r="J4" s="11">
+        <v>129230</v>
+      </c>
+      <c r="K4" s="11">
+        <v>129013</v>
+      </c>
+      <c r="L4" s="11">
+        <v>513183</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1741863</v>
+      </c>
+      <c r="N4" s="11">
+        <v>60432</v>
+      </c>
+      <c r="O4" s="13">
+        <v>88</v>
+      </c>
+      <c r="P4" s="13">
+        <v>96</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>82</v>
+      </c>
+      <c r="S4">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>46</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98AE077-C375-0E4D-89BD-544B6E37D2D2}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11E38BCC-59C8-0E46-8E65-C572EC7941F5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t>prep_oral</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>Eswatini</t>
+  </si>
+  <si>
+    <t>Kenya</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1135,60 @@
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>173981</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>13790</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>25199</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>88</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="T8">
+        <v>40.1</v>
+      </c>
+      <c r="U8">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>92</v>
+      </c>
+      <c r="Z8">
+        <v>92</v>
+      </c>
+      <c r="AA8">
+        <v>7</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11E38BCC-59C8-0E46-8E65-C572EC7941F5}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C9EE00-51CA-9740-82AF-100EEB8927D8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="-32820" yWindow="3660" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>prep_oral</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>Kenya</t>
+  </si>
+  <si>
+    <t>Ghana</t>
   </si>
 </sst>
 </file>
@@ -249,7 +252,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -301,12 +304,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -332,6 +348,15 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1191,7 +1216,60 @@
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>15395</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>95</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15">
+        <v>2163014</v>
+      </c>
+      <c r="J9" s="16">
+        <v>26329</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15">
+        <v>139054</v>
+      </c>
+      <c r="M9" s="14">
+        <v>480960</v>
+      </c>
+      <c r="N9" s="17">
+        <v>0</v>
+      </c>
+      <c r="O9" s="17">
+        <v>96</v>
+      </c>
+      <c r="P9" s="17">
+        <v>97</v>
+      </c>
+      <c r="R9">
+        <v>67</v>
+      </c>
+      <c r="S9">
+        <v>30</v>
+      </c>
+      <c r="T9">
+        <v>60</v>
+      </c>
+      <c r="U9">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C9EE00-51CA-9740-82AF-100EEB8927D8}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF33940D-B1A7-634B-AB05-2482FD5C76E5}"/>
   <bookViews>
     <workbookView xWindow="-32820" yWindow="3660" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -91,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
   <si>
     <t>prep_oral</t>
   </si>
@@ -199,6 +200,33 @@
   </si>
   <si>
     <t>Ghana</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>https://aidsinfo.unaids.org/</t>
+  </si>
+  <si>
+    <t>Hiv tetsing among pregnant women</t>
+  </si>
+  <si>
+    <t>ANC VL testing</t>
+  </si>
+  <si>
+    <t>https://www.nicd.ac.za/wp-content/uploads/2024/01/Antenatal-survey-2022-report_National_Provincial_12Jul2023_Clean_01.pdf</t>
+  </si>
+  <si>
+    <t>PNC VL testing</t>
+  </si>
+  <si>
+    <t>https://cquin.icap.columbia.edu/wp-content/uploads/2025/11/South-Africa-VTP-Poster_Nov-2025_Final-for-Print.pdf</t>
+  </si>
+  <si>
+    <t>Routine VL</t>
+  </si>
+  <si>
+    <t>https://www.differentiatedservicedelivery.org/wp-content/uploads/NDOH-Prevention-Treatment-Care-and-Support-Priorities-_-Gates-Foundation-Partners-Meeting-11-12-Feb-2516.pdf</t>
   </si>
 </sst>
 </file>
@@ -322,7 +350,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -354,9 +382,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1092,11 +1121,29 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="O6">
+        <v>73</v>
+      </c>
+      <c r="P6">
+        <v>87</v>
+      </c>
+      <c r="R6">
+        <v>80</v>
+      </c>
       <c r="S6">
         <v>95</v>
       </c>
       <c r="T6">
         <v>5</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>88.1</v>
+      </c>
+      <c r="Z6">
+        <v>46</v>
       </c>
       <c r="AA6">
         <v>66</v>
@@ -1732,4 +1779,74 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290418B9-1F0F-1140-BB8B-34C4D210D63F}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="18">
+        <v>0.73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>88.1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF33940D-B1A7-634B-AB05-2482FD5C76E5}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB8C1795-EFC0-DA46-9B56-828CF0ABCDAC}"/>
   <bookViews>
-    <workbookView xWindow="-32820" yWindow="3660" windowWidth="28800" windowHeight="15740" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,35 +63,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={2310EEF3-F49B-1740-9531-F7745180ADE8}</author>
-    <author>tc={D2460033-F738-7142-809A-6A6DE4B461DC}</author>
-  </authors>
-  <commentList>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{2310EEF3-F49B-1740-9531-F7745180ADE8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Community-Based HIV Test in 2025</t>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{D2460033-F738-7142-809A-6A6DE4B461DC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    90% HIV Ascertainment in STI services</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>prep_oral</t>
   </si>
@@ -736,17 +708,6 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K4" dT="2026-06-05T07:00:54.77" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{2310EEF3-F49B-1740-9531-F7745180ADE8}">
-    <text>Community-Based HIV Test in 2025</text>
-  </threadedComment>
-  <threadedComment ref="L4" dT="2026-06-05T07:06:08.87" personId="{5C421396-DDD7-7544-B72E-8164399E8CC5}" id="{D2460033-F738-7142-809A-6A6DE4B461DC}">
-    <text>90% HIV Ascertainment in STI services</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42369831-8138-B640-8215-2EE7ACAC45E9}">
   <dimension ref="A1:AB29"/>
@@ -1385,406 +1346,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15A684A-C287-EF40-83C7-44769AE087D6}">
-  <dimension ref="A1:AB29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="2">
-        <v>334817</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>147928</v>
-      </c>
-      <c r="E2">
-        <v>159303077</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>11237387</v>
-      </c>
-      <c r="J2" s="2">
-        <v>630566</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1064884</v>
-      </c>
-      <c r="L2" s="2">
-        <v>222182</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>1322885</v>
-      </c>
-      <c r="O2" s="4">
-        <v>90</v>
-      </c>
-      <c r="P2" s="4">
-        <v>95</v>
-      </c>
-      <c r="R2" s="5">
-        <v>67</v>
-      </c>
-      <c r="S2" s="5">
-        <v>37</v>
-      </c>
-      <c r="T2" s="5">
-        <v>40</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="V2" s="5">
-        <v>2</v>
-      </c>
-      <c r="W2" s="5">
-        <v>50</v>
-      </c>
-      <c r="X2" s="5">
-        <v>85</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>77</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>80</v>
-      </c>
-      <c r="AA2" s="5">
-        <v>24</v>
-      </c>
-      <c r="AB2" s="5"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6">
-        <v>133901</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1624</v>
-      </c>
-      <c r="D3" s="6">
-        <v>274325</v>
-      </c>
-      <c r="F3" s="8">
-        <v>6454</v>
-      </c>
-      <c r="G3">
-        <v>74</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>3671497</v>
-      </c>
-      <c r="J3" s="9">
-        <v>291365</v>
-      </c>
-      <c r="K3" s="9">
-        <v>516869</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>76</v>
-      </c>
-      <c r="P3" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>24</v>
-      </c>
-      <c r="R3">
-        <v>79</v>
-      </c>
-      <c r="S3">
-        <v>4</v>
-      </c>
-      <c r="T3">
-        <v>96</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>30</v>
-      </c>
-      <c r="W3">
-        <v>95</v>
-      </c>
-      <c r="X3">
-        <v>95</v>
-      </c>
-      <c r="AA3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="11">
-        <v>58089</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11">
-        <v>47890</v>
-      </c>
-      <c r="E4" s="11">
-        <v>139000000</v>
-      </c>
-      <c r="F4" s="12">
-        <v>32466</v>
-      </c>
-      <c r="G4" s="13">
-        <v>91</v>
-      </c>
-      <c r="H4" s="11">
-        <v>30762</v>
-      </c>
-      <c r="I4" s="11">
-        <v>3569803</v>
-      </c>
-      <c r="J4" s="11">
-        <v>129230</v>
-      </c>
-      <c r="K4" s="11">
-        <v>129013</v>
-      </c>
-      <c r="L4" s="11">
-        <v>513183</v>
-      </c>
-      <c r="M4" s="11">
-        <v>1741863</v>
-      </c>
-      <c r="N4" s="11">
-        <v>60432</v>
-      </c>
-      <c r="O4" s="13">
-        <v>88</v>
-      </c>
-      <c r="P4" s="13">
-        <v>96</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>15</v>
-      </c>
-      <c r="R4">
-        <v>82</v>
-      </c>
-      <c r="S4">
-        <v>47</v>
-      </c>
-      <c r="T4">
-        <v>46</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="AA4">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290418B9-1F0F-1140-BB8B-34C4D210D63F}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB8C1795-EFC0-DA46-9B56-828CF0ABCDAC}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="14_{78023D7A-79C9-BB4A-96DA-66D3AFB5E9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C572DB0-F928-534D-8DF4-0652EBE0DF45}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{B6C5909B-EEA9-8C48-8CDE-83CD703FC43E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="SA data" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>prep_oral</t>
   </si>
@@ -199,6 +199,24 @@
   </si>
   <si>
     <t>https://www.differentiatedservicedelivery.org/wp-content/uploads/NDOH-Prevention-Treatment-Care-and-Support-Priorities-_-Gates-Foundation-Partners-Meeting-11-12-Feb-2516.pdf</t>
+  </si>
+  <si>
+    <t>https://hst-assets-s3.s3.eu-north-1.amazonaws.com/publications/District-Health-Barometer-2024_2025.pdf</t>
+  </si>
+  <si>
+    <t>oral prep</t>
+  </si>
+  <si>
+    <t>https://www.spotlightnsp.co.za/2026/05/15/sas-arv-programme-hardly-grew-in-2025-according-to-latest-estimates/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vmmc </t>
+  </si>
+  <si>
+    <t>~290000</t>
+  </si>
+  <si>
+    <t>Thembisa 2025. https://www.spotlightnsp.co.za/hiv-dashboard/</t>
   </si>
 </sst>
 </file>
@@ -1082,6 +1100,15 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="B6">
+        <v>580000</v>
+      </c>
+      <c r="D6">
+        <v>290000</v>
+      </c>
+      <c r="E6">
+        <v>685663529</v>
+      </c>
       <c r="O6">
         <v>73</v>
       </c>
@@ -1347,11 +1374,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290418B9-1F0F-1140-BB8B-34C4D210D63F}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1414,6 +1441,39 @@
         <v>44</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>685663529</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>580000</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/country_baselines/Updated/country_baselines_summarised.xlsx
+++ b/data/country_baselines/Updated/country_baselines_summarised.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="SA data" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,6 +66,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
+    <t>country</t>
+  </si>
+  <si>
     <t>prep_oral</t>
   </si>
   <si>
@@ -145,9 +148,6 @@
   </si>
   <si>
     <t>ahd_package</t>
-  </si>
-  <si>
-    <t>country</t>
   </si>
   <si>
     <t>Mozambique</t>
@@ -227,7 +227,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -729,101 +729,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42369831-8138-B640-8215-2EE7ACAC45E9}">
   <dimension ref="A1:AB29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -898,7 +898,7 @@
       </c>
       <c r="AB2" s="5"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -972,7 +972,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" s="14"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -1306,64 +1306,64 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1">
       <c r="A20" s="1"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1">
       <c r="A29" s="1"/>
     </row>
   </sheetData>
@@ -1375,20 +1375,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290418B9-1F0F-1140-BB8B-34C4D210D63F}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="18">
         <v>0.73</v>
@@ -1397,7 +1397,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1441,9 +1441,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>685663529</v>
@@ -1452,7 +1452,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
